--- a/環境構成説明書_php.xlsx
+++ b/環境構成説明書_php.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miaozhixin/Desktop/MIAO/zuoye/ckwuser/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05F58056-0082-B74F-9946-20C228EF5C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1903FE-2BB7-884F-8DD2-374752120836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19200" xr2:uid="{FB4CCAFA-7A4A-BB4E-A06C-C05C25E21B7F}"/>
   </bookViews>
@@ -742,7 +742,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1">
